--- a/backend/exports/recruiters.xlsx
+++ b/backend/exports/recruiters.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H188"/>
+  <dimension ref="A1:H204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6476,13 +6476,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" t="inlineStr"/>
       <c r="B188" t="inlineStr">
         <is>
           <t>recruiting@ayratech.us</t>
         </is>
       </c>
-      <c r="C188" t="inlineStr"/>
       <c r="D188" t="inlineStr">
         <is>
           <t>Recruiter Post</t>
@@ -6506,6 +6504,520 @@
       <c r="H188" t="inlineStr">
         <is>
           <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>anil@asmtechsols.com</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Recruiter Post</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Hiring Lead</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/m-anil-kumar-b1687617a_hiring-nowhiring-seniorjavadeveloper-share-7493359395763040256-g7y9/?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAADhQOs4B9R75JmtI06nxLjXlROi13kELyKc</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>auto-extract</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>akshsingh@altimetrik.com</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Recruiter Post</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Hiring Lead</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/mahidhar07_hiring-java-spring-boot-developer-ctc-share-7493344610942066688-YxEH/?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAADhQOs4B9R75JmtI06nxLjXlROi13kELyKc</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>auto-extract</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Sachin.Tyagi@tanishasystems.com</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Recruiter Post</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Hiring Lead</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/sachin-tyagi-87343425_hi-one-of-our-client-is-looking-for-java-share-7493344360332431360-Je94/?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAADhQOs4B9R75JmtI06nxLjXlROi13kELyKc</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>auto-extract</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Geethak@staffworxs.com</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Recruiter Post</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Hiring Lead</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/geetha-khunchala-5764521b2_hiring-atlanta-georgia-share-7493400594028883968-1XmC/?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAADhQOs4B9R75JmtI06nxLjXlROi13kELyKc</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>auto-extract</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>kapil.kumar@opulentglobaltech.com</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Recruiter Post</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Hiring Lead</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/kapil-kumar-70067819a_hiring-peoplesoft-peoplesoftdeveloper-share-7493397845962809344-GjnK/?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAADhQOs4B9R75JmtI06nxLjXlROi13kELyKc</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>auto-extract</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>subash@northern-base.com</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Recruiter Post</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Hiring Lead</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/subash-ganapathi-a66476b3_java-javafullstack-fullstackdeveloper-share-7493387886797418496-dYpW/?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAADhQOs4B9R75JmtI06nxLjXlROi13kELyKc</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>auto-extract</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>rehman.s@careersoftusa.com</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Recruiter Post</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Hiring Lead</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/abdul-rehman-sheik-42a4b927b_shares-vendors-suppliers-share-7493400602727616512-eQVV/?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAADhQOs4B9R75JmtI06nxLjXlROi13kELyKc</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>auto-extract</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>+1 651-888-8786</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Recruiter Post</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Hiring Lead</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/bharadwaz-27b762191_hotlist-mail-job-share-7493419603830960129-jWg5/?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAADhQOs4B9R75JmtI06nxLjXlROi13kELyKc</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>auto-extract</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>navyatha.p@careersoft.com</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Recruiter Post</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Hiring Lead</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/navyatha-pothamsetty-258773349_shares-vendors-suppliers-share-7493674966345904128-9tVM/?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAADhQOs4B9R75JmtI06nxLjXlROi13kELyKc</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>auto-extract</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>hello@atlasdigitallab.com</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Recruiter Post</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Hiring Lead</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/paul-decarlis-1b98953b5_we-are-looking-for-motivated-individuals-share-7493768656108060672-nRHn/?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAADhQOs4B9R75JmtI06nxLjXlROi13kELyKc</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>auto-extract</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>amishra@globalitfamily.com</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Recruiter Post</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Hiring Lead</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/hiring-drupaldeveloper-drupal-share-7493782326749851648-DRb7/?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAADhQOs4B9R75JmtI06nxLjXlROi13kELyKc</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>auto-extract</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>business@thebaft.com</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Recruiter Post</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Hiring Lead</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/saket-borkar-a0669a248_hiring-baft-reactnative-share-7493982205040455681-iYPp/?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAADhQOs4B9R75JmtI06nxLjXlROi13kELyKc</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>auto-extract</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>abigailimah@outlook.com</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Recruiter Post</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Hiring Lead</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/abigail-imah-0ba547271_hiring-hiring-hiringgao-tek-unpaid-share-7494035346288979968-NDIV/?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAADhQOs4B9R75JmtI06nxLjXlROi13kELyKc</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>auto-extract</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>divya@vitsus.com</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Recruiter Post</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Hiring Lead</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/divya-dubey-32ba112b7_hiring-react-ui-developer-location-irving-share-7494054305210228738-sxPX/?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAADhQOs4B9R75JmtI06nxLjXlROi13kELyKc</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>auto-extract</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>sujal.j@voltoconsulting.com</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Recruiter Post</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Hiring Lead</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/sujal-recruiter_hiring-frontenddeveloper-reactdeveloper-share-7494060546351276032-P1wE/?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAADhQOs4B9R75JmtI06nxLjXlROi13kELyKc</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>auto-extract</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr"/>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>suneela@smartinfosolutions.tech</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr"/>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Recruiter Post</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Hiring Lead</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/suneela-raj-theerdhala-6a6465163_linkedinconnections-hiring-charlotte-share-7494080656608727040-iHit/?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAADhQOs4B9R75JmtI06nxLjXlROi13kELyKc</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>auto-extract</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
